--- a/reports/pdf_change_20261001.xlsx
+++ b/reports/pdf_change_20261001.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,035억   ·   현금 20억(0.4%)      당일 2026-10-01  vs  전영업일 2026-09-30      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,035억      당일 2026-10-01  vs  전영업일 2026-09-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -598,7 +598,7 @@
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,250억   ·   현금 38억(1.2%)      당일 2026-10-01  vs  전영업일 2026-09-30      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,250억      당일 2026-10-01  vs  전영업일 2026-09-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -622,7 +622,7 @@
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,723억   ·   현금 43억(1.6%)      당일 2026-10-01  vs  전영업일 2026-09-30      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,723억      당일 2026-10-01  vs  전영업일 2026-09-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -646,7 +646,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,988억   ·   현금 9억(0.5%)      당일 2026-10-01  vs  전영업일 2026-09-30      매수 2종목  /  매도 2종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,988억      당일 2026-10-01  vs  전영업일 2026-09-30      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -823,7 +823,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 308억   ·   현금 1억(0.5%)      당일 2026-10-01  vs  전영업일 2026-09-30      매수 2종목  /  매도 1종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 308억      당일 2026-10-01  vs  전영업일 2026-09-30      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -984,7 +984,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 474억   ·   현금 8억(1.6%)      당일 2026-10-01  vs  전영업일 2026-09-30      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 474억      당일 2026-10-01  vs  전영업일 2026-09-30      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
